--- a/artfynd/A 54008-2025 artfynd.xlsx
+++ b/artfynd/A 54008-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,6 +796,922 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129977064</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57734</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Slätmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>654612</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6683555</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129977140</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92055</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Slätmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>654676</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6683680</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129977065</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Slätmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>654591</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6683454</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129977127</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91602</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Slätmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>654676</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6683680</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129977055</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57734</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Slätmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>654640</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6683591</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129977117</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91566</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Slätmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>654649</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6683680</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Läderdoft.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129977222</v>
+      </c>
+      <c r="B9" t="n">
+        <v>75196</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Slätmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>654643</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6683509</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129977224</v>
+      </c>
+      <c r="B10" t="n">
+        <v>75196</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med isidier</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Slätmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>654676</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6683680</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54008-2025 artfynd.xlsx
+++ b/artfynd/A 54008-2025 artfynd.xlsx
@@ -1028,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129977065</v>
+        <v>129977127</v>
       </c>
       <c r="B5" t="n">
-        <v>57737</v>
+        <v>91602</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,35 +1039,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1075,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>654591</v>
+        <v>654676</v>
       </c>
       <c r="R5" t="n">
-        <v>6683454</v>
+        <v>6683680</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1110,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129977127</v>
+        <v>129977065</v>
       </c>
       <c r="B6" t="n">
-        <v>91602</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1158,26 +1149,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>654676</v>
+        <v>654591</v>
       </c>
       <c r="R6" t="n">
-        <v>6683680</v>
+        <v>6683454</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 54008-2025 artfynd.xlsx
+++ b/artfynd/A 54008-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>129977064</v>
       </c>
       <c r="B3" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>129977140</v>
       </c>
       <c r="B4" t="n">
-        <v>92055</v>
+        <v>92058</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>129977127</v>
       </c>
       <c r="B5" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>129977065</v>
       </c>
       <c r="B6" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>129977055</v>
       </c>
       <c r="B7" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>129977117</v>
       </c>
       <c r="B8" t="n">
-        <v>91566</v>
+        <v>91569</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>129977222</v>
       </c>
       <c r="B9" t="n">
-        <v>75196</v>
+        <v>75199</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>129977224</v>
       </c>
       <c r="B10" t="n">
-        <v>75196</v>
+        <v>75199</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 54008-2025 artfynd.xlsx
+++ b/artfynd/A 54008-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1713,6 +1713,701 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130018002</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98797</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Slätmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>654680</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6683340</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130017989</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58111</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Slätmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>654816</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6683279</v>
+      </c>
+      <c r="S12" t="n">
+        <v>40</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130017978</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Slätmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>654717</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6683326</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130017977</v>
+      </c>
+      <c r="B14" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Slätmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>654817</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6683310</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130017986</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Slätmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>654687</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6683336</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130017999</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92560</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Slätmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>654808</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6683254</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54008-2025 artfynd.xlsx
+++ b/artfynd/A 54008-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2408,6 +2408,327 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130044242</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Fågelmossen nordost, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>654557</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6683557</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130044244</v>
+      </c>
+      <c r="B18" t="n">
+        <v>96286</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dicranum flagellare</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Fågelmossen nordost, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>654594</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6683580</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130044240</v>
+      </c>
+      <c r="B19" t="n">
+        <v>43994</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Fågelmossen nordost, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>654694</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6683556</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54008-2025 artfynd.xlsx
+++ b/artfynd/A 54008-2025 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>129977140</v>
       </c>
       <c r="B4" t="n">
-        <v>92058</v>
+        <v>92059</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>129977127</v>
       </c>
       <c r="B5" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1376,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129977117</v>
+        <v>129977222</v>
       </c>
       <c r="B8" t="n">
-        <v>91569</v>
+        <v>75199</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,21 +1387,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>654649</v>
+        <v>654643</v>
       </c>
       <c r="R8" t="n">
-        <v>6683680</v>
+        <v>6683509</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1459,12 +1459,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Läderdoft.</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,10 +1486,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129977222</v>
+        <v>129977117</v>
       </c>
       <c r="B9" t="n">
-        <v>75199</v>
+        <v>91570</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,21 +1497,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1529,10 +1524,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654643</v>
+        <v>654649</v>
       </c>
       <c r="R9" t="n">
-        <v>6683509</v>
+        <v>6683680</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1564,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1569,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Läderdoft.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1718,7 +1718,7 @@
         <v>130018002</v>
       </c>
       <c r="B11" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2181,46 +2181,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130017986</v>
+        <v>130017999</v>
       </c>
       <c r="B15" t="n">
-        <v>57737</v>
+        <v>92561</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2228,10 +2219,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>654687</v>
+        <v>654808</v>
       </c>
       <c r="R15" t="n">
-        <v>6683336</v>
+        <v>6683254</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2263,7 +2254,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2273,7 +2264,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2300,37 +2291,46 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130017999</v>
+        <v>130017986</v>
       </c>
       <c r="B16" t="n">
-        <v>92560</v>
+        <v>57737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4769</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2338,10 +2338,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>654808</v>
+        <v>654687</v>
       </c>
       <c r="R16" t="n">
-        <v>6683254</v>
+        <v>6683336</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2413,7 +2413,7 @@
         <v>130044242</v>
       </c>
       <c r="B17" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>130044244</v>
       </c>
       <c r="B18" t="n">
-        <v>96286</v>
+        <v>96287</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 54008-2025 artfynd.xlsx
+++ b/artfynd/A 54008-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2181,37 +2181,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130017999</v>
+        <v>130017986</v>
       </c>
       <c r="B15" t="n">
-        <v>92561</v>
+        <v>57737</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4769</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2219,10 +2228,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>654808</v>
+        <v>654687</v>
       </c>
       <c r="R15" t="n">
-        <v>6683254</v>
+        <v>6683336</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2254,7 +2263,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2264,7 +2273,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,46 +2300,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130017986</v>
+        <v>130017999</v>
       </c>
       <c r="B16" t="n">
-        <v>57737</v>
+        <v>92561</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>4769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2338,10 +2338,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>654687</v>
+        <v>654808</v>
       </c>
       <c r="R16" t="n">
-        <v>6683336</v>
+        <v>6683254</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2729,6 +2729,1297 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130072895</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Slätmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>654644</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6683708</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>130072893</v>
+      </c>
+      <c r="B21" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Slätmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>654738</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6683415</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130072909</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98802</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Slätmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>654637</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6683704</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>130072899</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58111</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Slätmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>654605</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6683731</v>
+      </c>
+      <c r="S23" t="n">
+        <v>35</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130072906</v>
+      </c>
+      <c r="B24" t="n">
+        <v>96244</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>210</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Slätmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>654739</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6683420</v>
+      </c>
+      <c r="S24" t="n">
+        <v>4</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130072910</v>
+      </c>
+      <c r="B25" t="n">
+        <v>105868</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Slätmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>654756</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6683374</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Uppskattat antal. De täcker ett par kvadratmeter.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130072911</v>
+      </c>
+      <c r="B26" t="n">
+        <v>105868</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Slätmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>654631</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6683633</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130072907</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98802</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Slätmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>654639</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6683692</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Räknade en och en.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>130072894</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Slätmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>654633</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6683514</v>
+      </c>
+      <c r="S28" t="n">
+        <v>4</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>130072905</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91383</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Slätmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>654636</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6683511</v>
+      </c>
+      <c r="S29" t="n">
+        <v>4</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>130072897</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58111</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Slätmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>654636</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6683511</v>
+      </c>
+      <c r="S30" t="n">
+        <v>4</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54008-2025 artfynd.xlsx
+++ b/artfynd/A 54008-2025 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>129977140</v>
       </c>
       <c r="B4" t="n">
-        <v>92059</v>
+        <v>92076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129977127</v>
+        <v>129977065</v>
       </c>
       <c r="B5" t="n">
-        <v>91606</v>
+        <v>57740</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,26 +1039,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1066,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>654676</v>
+        <v>654591</v>
       </c>
       <c r="R5" t="n">
-        <v>6683680</v>
+        <v>6683454</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1101,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129977065</v>
+        <v>129977127</v>
       </c>
       <c r="B6" t="n">
-        <v>57740</v>
+        <v>91623</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1149,35 +1158,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>654591</v>
+        <v>654676</v>
       </c>
       <c r="R6" t="n">
-        <v>6683454</v>
+        <v>6683680</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1379,7 +1379,7 @@
         <v>129977222</v>
       </c>
       <c r="B8" t="n">
-        <v>75199</v>
+        <v>75200</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>129977117</v>
       </c>
       <c r="B9" t="n">
-        <v>91570</v>
+        <v>91587</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>129977224</v>
       </c>
       <c r="B10" t="n">
-        <v>75199</v>
+        <v>75200</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>130018002</v>
       </c>
       <c r="B11" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>130017989</v>
       </c>
       <c r="B12" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2181,46 +2181,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130017986</v>
+        <v>130017999</v>
       </c>
       <c r="B15" t="n">
-        <v>57737</v>
+        <v>92578</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2228,10 +2219,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>654687</v>
+        <v>654808</v>
       </c>
       <c r="R15" t="n">
-        <v>6683336</v>
+        <v>6683254</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2263,7 +2254,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2273,7 +2264,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2300,37 +2291,46 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130017999</v>
+        <v>130017986</v>
       </c>
       <c r="B16" t="n">
-        <v>92561</v>
+        <v>57737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4769</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2338,10 +2338,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>654808</v>
+        <v>654687</v>
       </c>
       <c r="R16" t="n">
-        <v>6683254</v>
+        <v>6683336</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2413,7 +2413,7 @@
         <v>130044242</v>
       </c>
       <c r="B17" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>130044244</v>
       </c>
       <c r="B18" t="n">
-        <v>96287</v>
+        <v>96304</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>130072909</v>
       </c>
       <c r="B22" t="n">
-        <v>98802</v>
+        <v>98815</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>130072899</v>
       </c>
       <c r="B23" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3200,10 +3200,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130072906</v>
+        <v>130072910</v>
       </c>
       <c r="B24" t="n">
-        <v>96244</v>
+        <v>105881</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3211,25 +3211,33 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>210</v>
+        <v>221144</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
@@ -3239,10 +3247,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>654739</v>
+        <v>654756</v>
       </c>
       <c r="R24" t="n">
-        <v>6683420</v>
+        <v>6683374</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3274,7 +3282,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3284,7 +3292,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Uppskattat antal. De täcker ett par kvadratmeter.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3311,10 +3324,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130072910</v>
+        <v>130072906</v>
       </c>
       <c r="B25" t="n">
-        <v>105868</v>
+        <v>96257</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3322,33 +3335,25 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>210</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -3358,10 +3363,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>654756</v>
+        <v>654739</v>
       </c>
       <c r="R25" t="n">
-        <v>6683374</v>
+        <v>6683420</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3393,7 +3398,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3403,12 +3408,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:58</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Uppskattat antal. De täcker ett par kvadratmeter.</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3438,7 +3438,7 @@
         <v>130072911</v>
       </c>
       <c r="B26" t="n">
-        <v>105868</v>
+        <v>105881</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>130072907</v>
       </c>
       <c r="B27" t="n">
-        <v>98802</v>
+        <v>98815</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3678,46 +3678,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130072894</v>
+        <v>130072905</v>
       </c>
       <c r="B28" t="n">
-        <v>57737</v>
+        <v>91396</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>3215</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3725,10 +3716,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>654633</v>
+        <v>654636</v>
       </c>
       <c r="R28" t="n">
-        <v>6683514</v>
+        <v>6683511</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3760,7 +3751,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3770,7 +3761,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3797,37 +3788,46 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130072905</v>
+        <v>130072894</v>
       </c>
       <c r="B29" t="n">
-        <v>91383</v>
+        <v>57737</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3215</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>654636</v>
+        <v>654633</v>
       </c>
       <c r="R29" t="n">
-        <v>6683511</v>
+        <v>6683514</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3910,7 +3910,7 @@
         <v>130072897</v>
       </c>
       <c r="B30" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 54008-2025 artfynd.xlsx
+++ b/artfynd/A 54008-2025 artfynd.xlsx
@@ -2850,46 +2850,43 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130072909</v>
+        <v>130072893</v>
       </c>
       <c r="B21" t="n">
-        <v>98831</v>
+        <v>5197</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2897,10 +2894,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>654637</v>
+        <v>654738</v>
       </c>
       <c r="R21" t="n">
-        <v>6683704</v>
+        <v>6683415</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -2932,7 +2929,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2942,7 +2939,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2969,43 +2966,46 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130072893</v>
+        <v>130072909</v>
       </c>
       <c r="B22" t="n">
-        <v>5197</v>
+        <v>98831</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3013,10 +3013,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>654738</v>
+        <v>654637</v>
       </c>
       <c r="R22" t="n">
-        <v>6683415</v>
+        <v>6683704</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 54008-2025 artfynd.xlsx
+++ b/artfynd/A 54008-2025 artfynd.xlsx
@@ -2850,43 +2850,46 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130072893</v>
+        <v>130072909</v>
       </c>
       <c r="B21" t="n">
-        <v>5197</v>
+        <v>98831</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2894,10 +2897,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>654738</v>
+        <v>654637</v>
       </c>
       <c r="R21" t="n">
-        <v>6683415</v>
+        <v>6683704</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -2929,7 +2932,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2939,7 +2942,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2966,46 +2969,43 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130072909</v>
+        <v>130072893</v>
       </c>
       <c r="B22" t="n">
-        <v>98831</v>
+        <v>5197</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3013,10 +3013,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>654637</v>
+        <v>654738</v>
       </c>
       <c r="R22" t="n">
-        <v>6683704</v>
+        <v>6683415</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 54008-2025 artfynd.xlsx
+++ b/artfynd/A 54008-2025 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>129977140</v>
       </c>
       <c r="B4" t="n">
-        <v>92092</v>
+        <v>92094</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>129977127</v>
       </c>
       <c r="B5" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>129977117</v>
       </c>
       <c r="B8" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>130018002</v>
       </c>
       <c r="B11" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>130017999</v>
       </c>
       <c r="B16" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>130044244</v>
       </c>
       <c r="B18" t="n">
-        <v>96320</v>
+        <v>96322</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>130072909</v>
       </c>
       <c r="B21" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3200,10 +3200,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130072906</v>
+        <v>130072910</v>
       </c>
       <c r="B24" t="n">
-        <v>96273</v>
+        <v>105900</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3211,25 +3211,33 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>210</v>
+        <v>221144</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
@@ -3239,10 +3247,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>654739</v>
+        <v>654756</v>
       </c>
       <c r="R24" t="n">
-        <v>6683420</v>
+        <v>6683374</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3274,7 +3282,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3284,7 +3292,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Uppskattat antal. De täcker ett par kvadratmeter.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3311,10 +3324,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130072910</v>
+        <v>130072906</v>
       </c>
       <c r="B25" t="n">
-        <v>105897</v>
+        <v>96275</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3322,33 +3335,25 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>210</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -3358,10 +3363,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>654756</v>
+        <v>654739</v>
       </c>
       <c r="R25" t="n">
-        <v>6683374</v>
+        <v>6683420</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3393,7 +3398,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3403,12 +3408,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:58</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Uppskattat antal. De täcker ett par kvadratmeter.</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3435,42 +3435,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130072907</v>
+        <v>130072911</v>
       </c>
       <c r="B26" t="n">
-        <v>98831</v>
+        <v>105900</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>654639</v>
+        <v>654631</v>
       </c>
       <c r="R26" t="n">
-        <v>6683692</v>
+        <v>6683633</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3527,12 +3527,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:34</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Räknade en och en.</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3559,42 +3554,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130072911</v>
+        <v>130072907</v>
       </c>
       <c r="B27" t="n">
-        <v>105897</v>
+        <v>98833</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -3606,10 +3601,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>654631</v>
+        <v>654639</v>
       </c>
       <c r="R27" t="n">
-        <v>6683633</v>
+        <v>6683692</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3641,7 +3636,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3651,7 +3646,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Räknade en och en.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3800,7 +3800,7 @@
         <v>130072905</v>
       </c>
       <c r="B29" t="n">
-        <v>91412</v>
+        <v>91414</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 54008-2025 artfynd.xlsx
+++ b/artfynd/A 54008-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>129977064</v>
       </c>
       <c r="B3" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>129977140</v>
       </c>
       <c r="B4" t="n">
-        <v>92094</v>
+        <v>92181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129977127</v>
+        <v>129977065</v>
       </c>
       <c r="B5" t="n">
-        <v>91641</v>
+        <v>57826</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,26 +1039,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1066,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>654676</v>
+        <v>654591</v>
       </c>
       <c r="R5" t="n">
-        <v>6683680</v>
+        <v>6683454</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1101,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129977065</v>
+        <v>129977127</v>
       </c>
       <c r="B6" t="n">
-        <v>57741</v>
+        <v>91728</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1149,35 +1158,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>654591</v>
+        <v>654676</v>
       </c>
       <c r="R6" t="n">
-        <v>6683454</v>
+        <v>6683680</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,7 +1260,7 @@
         <v>129977055</v>
       </c>
       <c r="B7" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>129977117</v>
       </c>
       <c r="B8" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>129977222</v>
       </c>
       <c r="B9" t="n">
-        <v>75201</v>
+        <v>75286</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>129977224</v>
       </c>
       <c r="B10" t="n">
-        <v>75201</v>
+        <v>75286</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>130018002</v>
       </c>
       <c r="B11" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>130017989</v>
       </c>
       <c r="B12" t="n">
-        <v>58113</v>
+        <v>58198</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2181,46 +2181,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130017986</v>
+        <v>130017999</v>
       </c>
       <c r="B15" t="n">
-        <v>57738</v>
+        <v>92683</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2228,10 +2219,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>654687</v>
+        <v>654808</v>
       </c>
       <c r="R15" t="n">
-        <v>6683336</v>
+        <v>6683254</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2263,7 +2254,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2273,7 +2264,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2300,37 +2291,46 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130017999</v>
+        <v>130017986</v>
       </c>
       <c r="B16" t="n">
-        <v>92596</v>
+        <v>57823</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4769</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2338,10 +2338,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>654808</v>
+        <v>654687</v>
       </c>
       <c r="R16" t="n">
-        <v>6683254</v>
+        <v>6683336</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2413,7 +2413,7 @@
         <v>130044242</v>
       </c>
       <c r="B17" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>130044244</v>
       </c>
       <c r="B18" t="n">
-        <v>96322</v>
+        <v>96409</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>130044240</v>
       </c>
       <c r="B19" t="n">
-        <v>43995</v>
+        <v>44080</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>130072895</v>
       </c>
       <c r="B20" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2850,46 +2850,43 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130072909</v>
+        <v>130072893</v>
       </c>
       <c r="B21" t="n">
-        <v>98833</v>
+        <v>5197</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2897,10 +2894,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>654637</v>
+        <v>654738</v>
       </c>
       <c r="R21" t="n">
-        <v>6683704</v>
+        <v>6683415</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -2932,7 +2929,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2942,7 +2939,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2969,43 +2966,46 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130072893</v>
+        <v>130072909</v>
       </c>
       <c r="B22" t="n">
-        <v>5197</v>
+        <v>98920</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3013,10 +3013,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>654738</v>
+        <v>654637</v>
       </c>
       <c r="R22" t="n">
-        <v>6683415</v>
+        <v>6683704</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3088,7 +3088,7 @@
         <v>130072899</v>
       </c>
       <c r="B23" t="n">
-        <v>58113</v>
+        <v>58198</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>130072910</v>
       </c>
       <c r="B24" t="n">
-        <v>105900</v>
+        <v>105987</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>130072906</v>
       </c>
       <c r="B25" t="n">
-        <v>96275</v>
+        <v>96362</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>130072911</v>
       </c>
       <c r="B26" t="n">
-        <v>105900</v>
+        <v>105987</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>130072907</v>
       </c>
       <c r="B27" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>130072894</v>
       </c>
       <c r="B28" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>130072905</v>
       </c>
       <c r="B29" t="n">
-        <v>91414</v>
+        <v>91501</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>130072897</v>
       </c>
       <c r="B30" t="n">
-        <v>58113</v>
+        <v>58198</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 54008-2025 artfynd.xlsx
+++ b/artfynd/A 54008-2025 artfynd.xlsx
@@ -1376,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129977117</v>
+        <v>129977222</v>
       </c>
       <c r="B8" t="n">
-        <v>91692</v>
+        <v>75286</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,21 +1387,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>654649</v>
+        <v>654643</v>
       </c>
       <c r="R8" t="n">
-        <v>6683680</v>
+        <v>6683509</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1459,12 +1459,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Läderdoft.</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,10 +1486,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129977222</v>
+        <v>129977117</v>
       </c>
       <c r="B9" t="n">
-        <v>75286</v>
+        <v>91692</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,21 +1497,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1529,10 +1524,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654643</v>
+        <v>654649</v>
       </c>
       <c r="R9" t="n">
-        <v>6683509</v>
+        <v>6683680</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1564,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1569,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Läderdoft.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -3200,10 +3200,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130072910</v>
+        <v>130072906</v>
       </c>
       <c r="B24" t="n">
-        <v>105987</v>
+        <v>96362</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3211,33 +3211,25 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221144</v>
+        <v>210</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
@@ -3247,10 +3239,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>654756</v>
+        <v>654739</v>
       </c>
       <c r="R24" t="n">
-        <v>6683374</v>
+        <v>6683420</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3282,7 +3274,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3292,12 +3284,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:58</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Uppskattat antal. De täcker ett par kvadratmeter.</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3324,10 +3311,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130072906</v>
+        <v>130072910</v>
       </c>
       <c r="B25" t="n">
-        <v>96362</v>
+        <v>105987</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3335,25 +3322,33 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>210</v>
+        <v>221144</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -3363,10 +3358,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>654739</v>
+        <v>654756</v>
       </c>
       <c r="R25" t="n">
-        <v>6683420</v>
+        <v>6683374</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3398,7 +3393,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3408,7 +3403,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Uppskattat antal. De täcker ett par kvadratmeter.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3435,42 +3435,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130072911</v>
+        <v>130072907</v>
       </c>
       <c r="B26" t="n">
-        <v>105987</v>
+        <v>98920</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>654631</v>
+        <v>654639</v>
       </c>
       <c r="R26" t="n">
-        <v>6683633</v>
+        <v>6683692</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3527,7 +3527,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Räknade en och en.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3554,42 +3559,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130072907</v>
+        <v>130072911</v>
       </c>
       <c r="B27" t="n">
-        <v>98920</v>
+        <v>105987</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -3601,10 +3606,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>654639</v>
+        <v>654631</v>
       </c>
       <c r="R27" t="n">
-        <v>6683692</v>
+        <v>6683633</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3636,7 +3641,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3646,12 +3651,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:34</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Räknade en och en.</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3678,46 +3678,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130072894</v>
+        <v>130072905</v>
       </c>
       <c r="B28" t="n">
-        <v>57823</v>
+        <v>91501</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>3215</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3725,10 +3716,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>654633</v>
+        <v>654636</v>
       </c>
       <c r="R28" t="n">
-        <v>6683514</v>
+        <v>6683511</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3760,7 +3751,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3770,7 +3761,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3797,37 +3788,46 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130072905</v>
+        <v>130072894</v>
       </c>
       <c r="B29" t="n">
-        <v>91501</v>
+        <v>57823</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3215</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>654636</v>
+        <v>654633</v>
       </c>
       <c r="R29" t="n">
-        <v>6683511</v>
+        <v>6683514</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 54008-2025 artfynd.xlsx
+++ b/artfynd/A 54008-2025 artfynd.xlsx
@@ -1028,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129977065</v>
+        <v>129977127</v>
       </c>
       <c r="B5" t="n">
-        <v>57826</v>
+        <v>91728</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,35 +1039,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1075,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>654591</v>
+        <v>654676</v>
       </c>
       <c r="R5" t="n">
-        <v>6683454</v>
+        <v>6683680</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1110,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129977127</v>
+        <v>129977065</v>
       </c>
       <c r="B6" t="n">
-        <v>91728</v>
+        <v>57826</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1158,26 +1149,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>654676</v>
+        <v>654591</v>
       </c>
       <c r="R6" t="n">
-        <v>6683680</v>
+        <v>6683454</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1376,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129977222</v>
+        <v>129977117</v>
       </c>
       <c r="B8" t="n">
-        <v>75286</v>
+        <v>91692</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,21 +1387,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>654643</v>
+        <v>654649</v>
       </c>
       <c r="R8" t="n">
-        <v>6683509</v>
+        <v>6683680</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1459,7 +1459,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Läderdoft.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129977117</v>
+        <v>129977222</v>
       </c>
       <c r="B9" t="n">
-        <v>91692</v>
+        <v>75286</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1497,21 +1502,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1524,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654649</v>
+        <v>654643</v>
       </c>
       <c r="R9" t="n">
-        <v>6683680</v>
+        <v>6683509</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1559,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,12 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Läderdoft.</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2181,37 +2181,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130017999</v>
+        <v>130017986</v>
       </c>
       <c r="B15" t="n">
-        <v>92683</v>
+        <v>57823</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4769</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2219,10 +2228,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>654808</v>
+        <v>654687</v>
       </c>
       <c r="R15" t="n">
-        <v>6683254</v>
+        <v>6683336</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2254,7 +2263,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2264,7 +2273,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,46 +2300,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130017986</v>
+        <v>130017999</v>
       </c>
       <c r="B16" t="n">
-        <v>57823</v>
+        <v>92683</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>4769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2338,10 +2338,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>654687</v>
+        <v>654808</v>
       </c>
       <c r="R16" t="n">
-        <v>6683336</v>
+        <v>6683254</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3200,10 +3200,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130072906</v>
+        <v>130072910</v>
       </c>
       <c r="B24" t="n">
-        <v>96362</v>
+        <v>105987</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3211,25 +3211,33 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>210</v>
+        <v>221144</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
@@ -3239,10 +3247,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>654739</v>
+        <v>654756</v>
       </c>
       <c r="R24" t="n">
-        <v>6683420</v>
+        <v>6683374</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3274,7 +3282,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3284,7 +3292,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Uppskattat antal. De täcker ett par kvadratmeter.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3311,10 +3324,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130072910</v>
+        <v>130072906</v>
       </c>
       <c r="B25" t="n">
-        <v>105987</v>
+        <v>96362</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3322,33 +3335,25 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>210</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -3358,10 +3363,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>654756</v>
+        <v>654739</v>
       </c>
       <c r="R25" t="n">
-        <v>6683374</v>
+        <v>6683420</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3393,7 +3398,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3403,12 +3408,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:58</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Uppskattat antal. De täcker ett par kvadratmeter.</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3678,37 +3678,46 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130072905</v>
+        <v>130072894</v>
       </c>
       <c r="B28" t="n">
-        <v>91501</v>
+        <v>57823</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3215</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3716,10 +3725,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>654636</v>
+        <v>654633</v>
       </c>
       <c r="R28" t="n">
-        <v>6683511</v>
+        <v>6683514</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3751,7 +3760,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3761,7 +3770,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3788,46 +3797,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130072894</v>
+        <v>130072905</v>
       </c>
       <c r="B29" t="n">
-        <v>57823</v>
+        <v>91501</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>3215</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>654633</v>
+        <v>654636</v>
       </c>
       <c r="R29" t="n">
-        <v>6683514</v>
+        <v>6683511</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 54008-2025 artfynd.xlsx
+++ b/artfynd/A 54008-2025 artfynd.xlsx
@@ -2850,43 +2850,46 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130072893</v>
+        <v>130072909</v>
       </c>
       <c r="B21" t="n">
-        <v>5197</v>
+        <v>98920</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2894,10 +2897,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>654738</v>
+        <v>654637</v>
       </c>
       <c r="R21" t="n">
-        <v>6683415</v>
+        <v>6683704</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -2929,7 +2932,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2939,7 +2942,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2966,46 +2969,43 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130072909</v>
+        <v>130072893</v>
       </c>
       <c r="B22" t="n">
-        <v>98920</v>
+        <v>5197</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3013,10 +3013,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>654637</v>
+        <v>654738</v>
       </c>
       <c r="R22" t="n">
-        <v>6683704</v>
+        <v>6683415</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3200,10 +3200,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130072910</v>
+        <v>130072906</v>
       </c>
       <c r="B24" t="n">
-        <v>105987</v>
+        <v>96362</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3211,33 +3211,25 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221144</v>
+        <v>210</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
@@ -3247,10 +3239,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>654756</v>
+        <v>654739</v>
       </c>
       <c r="R24" t="n">
-        <v>6683374</v>
+        <v>6683420</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3282,7 +3274,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3292,12 +3284,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:58</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Uppskattat antal. De täcker ett par kvadratmeter.</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3324,10 +3311,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130072906</v>
+        <v>130072910</v>
       </c>
       <c r="B25" t="n">
-        <v>96362</v>
+        <v>105987</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3335,25 +3322,33 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>210</v>
+        <v>221144</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -3363,10 +3358,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>654739</v>
+        <v>654756</v>
       </c>
       <c r="R25" t="n">
-        <v>6683420</v>
+        <v>6683374</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3398,7 +3393,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3408,7 +3403,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Uppskattat antal. De täcker ett par kvadratmeter.</t>
         </is>
       </c>
       <c r="AD25" t="b">
